--- a/artfynd/S 3415-2025 artfynd.xlsx
+++ b/artfynd/S 3415-2025 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>134700162</v>
       </c>
       <c r="B4" t="n">
-        <v>92647</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,6 +1014,21 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog barr/ädellöv.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
